--- a/gd/excel/item_type.xlsx
+++ b/gd/excel/item_type.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,66 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>防具</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>消耗品</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A4:C1000">
     <cfRule type="expression" priority="1" dxfId="0">

--- a/gd/excel/item_type.xlsx
+++ b/gd/excel/item_type.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,19 +32,13 @@
       <sz val="12"/>
     </font>
     <font>
-      <name val="Consolas"/>
-      <i val="1"/>
-      <color rgb="001B4332"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="微软雅黑"/>
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,12 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C9A227"/>
         <bgColor rgb="00C9A227"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8F3DC"/>
-        <bgColor rgb="00D8F3DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,18 +82,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -507,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -515,119 +500,97 @@
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>id</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">name
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>string[i18n]</t>
+          </r>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">code
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>string</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>类型唯一ID，禁止修改</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>string[i18n]</t>
+          <t>类型名称（多语言）</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>类型唯一ID，禁止修改</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>类型名称（多语言）</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>类型代码，程序引用用</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>武器</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>防具</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>armor</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>消耗品</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>consumable</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>材料</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-    </row>
+    <row r="3"/>
   </sheetData>
-  <conditionalFormatting sqref="A4:C1000">
+  <conditionalFormatting sqref="A3:C1000">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
